--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +77,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,11 +95,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12081,7 +12099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12125,6 +12143,57 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0021</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2006_07_0021 'Baráž o Extraligu' (L15, parent=NODE_S2006_07_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0028</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2006_07_0028 'Baráž o I.ligu' (L25, parent=NODE_S2006_07_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0039</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2006_07_0039 'O postup do I.ligy' (L25, parent=NODE_S2006_07_0033) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -15359,8 +15428,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -15440,7 +15507,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -28539,6 +28605,127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0021</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2006_07_0021 'Baráž o Extraligu' (L15, parent=NODE_S2006_07_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0028</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2006_07_0028 'Baráž o I.ligu' (L25, parent=NODE_S2006_07_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0039</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2006_07_0039 'O postup do I.ligy' (L25, parent=NODE_S2006_07_0033) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10083,11 +10083,6 @@
           <t>CLUB_S2006_07_0183</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0188</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>setrval</t>
@@ -10164,11 +10159,6 @@
       <c r="Q8" t="inlineStr">
         <is>
           <t>CLUB_S2006_07_0184</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0188</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -11994,11 +11984,6 @@
           <t>CLUB_S2006_07_0200</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0188</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>reorganizace</t>
@@ -12099,7 +12084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12147,14 +12132,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NODE_S2006_07_0021</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2006_07_0021 'Baráž o Extraligu' (L15, parent=NODE_S2006_07_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12164,14 +12144,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S2006_07_0028</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2006_07_0028 'Baráž o I.ligu' (L25, parent=NODE_S2006_07_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -12181,17 +12156,348 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S2006_07_0039</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2006_07_0039 'O postup do I.ligy' (L25, parent=NODE_S2006_07_0033) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Felbabka' → 'Králův Dvůr' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2005_06_0148 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -15428,6 +15734,8 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -15458,6 +15766,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0001</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -15470,6 +15783,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0003</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -15482,6 +15800,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0003</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -15494,6 +15817,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0033</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -15507,6 +15835,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -20493,12 +20822,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -20787,12 +21116,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -20997,12 +21326,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -21081,12 +21410,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -21123,12 +21452,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -21501,12 +21830,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň.</t>
+          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň. || TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sportovní klub Kadaň</t>
+          <t>Kadaň</t>
         </is>
       </c>
     </row>
@@ -21617,12 +21946,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -22069,12 +22398,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -22111,12 +22440,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -22756,12 +23085,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -23050,12 +23379,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -23784,12 +24113,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -24078,12 +24407,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Felbabka = TJ Sokol Felbabka (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). 'BER' = Beroun skupina. city Felbabka.</t>
+          <t>Felbabka = TJ Sokol Felbabka (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). 'BER' = Beroun skupina. city Felbabka. || TBD: city 'Felbabka' → 'Králův Dvůr' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Felbabka</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -24120,12 +24449,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -24629,12 +24958,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -24755,12 +25084,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -25936,12 +26265,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26556,12 +26885,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka.</t>
+          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka. || TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>BK JTC Nová Paka</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -26776,12 +27105,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -27243,12 +27572,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou.</t>
+          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou. || TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>SB Světlá nad Sázavou</t>
+          <t>Světlá nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -27579,12 +27908,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -27698,14 +28027,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0188</t>
-        </is>
-      </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -27745,14 +28069,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0188</t>
-        </is>
-      </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -27920,12 +28239,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno.</t>
+          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno. || TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>HLC Bulldogs Brno</t>
+          <t>Bulldogs Brno</t>
         </is>
       </c>
     </row>
@@ -28051,12 +28370,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -28348,14 +28667,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0188</t>
-        </is>
-      </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -28611,11 +28925,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -28660,21 +28974,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S2006_07_0021</t>
+          <t>CLUB_S2006_07_0003</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2006_07_0021 'Baráž o Extraligu' (L15, parent=NODE_S2006_07_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -28682,21 +28994,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S2006_07_0028</t>
+          <t>CLUB_S2006_07_0010</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2006_07_0028 'Baráž o I.ligu' (L25, parent=NODE_S2006_07_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -28704,24 +29014,582 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S2006_07_0039</t>
+          <t>CLUB_S2006_07_0015</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2006_07_0039 'O postup do I.ligy' (L25, parent=NODE_S2006_07_0033) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0017</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0018</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0027</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0032</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0043</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0044</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0059</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0066</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0083</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0090</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Felbabka' → 'Králův Dvůr' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0091</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0103</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0103</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0106</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0120</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0136</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0141</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2005_06_0148 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0146</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0152</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0157</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0168</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0171</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0180</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0183</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0184</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0188</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0191</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S2006_07_0200</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35021,6 +35889,11 @@
           <t>CLUB_S2005_06_0095</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>TR_S2006_07_00084</t>

--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0036</t>
+          <t>CLUB_S2005_06_0166</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0036</t>
+          <t>CLUB_S2005_06_0166</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -12084,7 +12084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12134,7 +12134,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12146,7 +12146,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -12158,7 +12158,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12170,7 +12170,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12182,7 +12182,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12194,7 +12194,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -12206,7 +12206,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12230,7 +12230,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12242,7 +12242,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2005_06_0148 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12266,7 +12266,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12278,7 +12278,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Felbabka' → 'Králův Dvůr' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12290,7 +12290,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -12302,7 +12302,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S2005_06_0166 'HC Chotěboř (STČ)'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12314,7 +12314,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12338,7 +12338,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12350,7 +12350,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12362,7 +12362,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2005_06_0148 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12374,130 +12374,10 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -12514,7 +12394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12573,6 +12453,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12615,6 +12500,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC Sparta Praha.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12662,6 +12552,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12704,6 +12599,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12746,6 +12646,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12788,6 +12693,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12830,6 +12740,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12872,6 +12787,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12914,6 +12834,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12956,6 +12881,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12998,6 +12928,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13040,6 +12975,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13082,6 +13022,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13124,6 +13069,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13166,6 +13116,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13208,6 +13163,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13250,6 +13210,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13292,6 +13257,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13334,6 +13304,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13376,6 +13351,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13418,6 +13398,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13460,6 +13445,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13502,6 +13492,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13544,6 +13539,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13586,6 +13586,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13628,6 +13633,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13670,6 +13680,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13712,6 +13727,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13801,6 +13821,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13843,6 +13868,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13969,6 +13999,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0036</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -14011,6 +14046,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0037</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14053,6 +14093,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0038</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -14095,6 +14140,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0039</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -14137,6 +14187,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0040</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14179,6 +14234,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0041</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14221,6 +14281,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0042</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14263,6 +14328,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0043</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14305,6 +14375,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0044</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14347,6 +14422,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0045</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14389,6 +14469,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0046</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14431,6 +14516,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0047</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14473,6 +14563,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0048</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14599,6 +14694,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0049</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14641,6 +14741,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0051</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14809,6 +14914,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0061</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -14851,6 +14961,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0062</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -14893,6 +15008,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0055</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -14935,6 +15055,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0063</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -14977,6 +15102,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0064</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15229,6 +15359,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0066</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -15271,6 +15406,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0067</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -15439,6 +15579,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0070</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -15481,6 +15626,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0071</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -15523,6 +15673,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0072</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -15731,6 +15886,11 @@
       <c r="K76" t="inlineStr">
         <is>
           <t>Kontejner L40</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0077</t>
         </is>
       </c>
     </row>
@@ -15754,6 +15914,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -15771,6 +15936,11 @@
           <t>NODE_S2006_07_0001</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -15788,6 +15958,11 @@
           <t>NODE_S2006_07_0003</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -15805,6 +15980,11 @@
           <t>NODE_S2006_07_0003</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -15822,6 +16002,11 @@
           <t>NODE_S2006_07_0033</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -15832,6 +16017,11 @@
       <c r="B85" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -20822,12 +21012,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -21326,12 +21516,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -21410,12 +21600,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -21946,12 +22136,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -24113,12 +24303,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -24407,12 +24597,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Felbabka = TJ Sokol Felbabka (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). 'BER' = Beroun skupina. city Felbabka. || TBD: city 'Felbabka' → 'Králův Dvůr' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Felbabka = TJ Sokol Felbabka (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). 'BER' = Beroun skupina. city Felbabka.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Králův Dvůr</t>
+          <t>Felbabka</t>
         </is>
       </c>
     </row>
@@ -24449,12 +24639,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -24958,12 +25148,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -25084,12 +25274,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -27315,12 +27505,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0036</t>
+          <t>CLUB_S2005_06_0166</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>B-tým Spartak Chotěboř (CLUB_S1953_54_0316). Přejmenováno II → B (D21). prev na 52/53 0263 (A-tým, B 52/53 neexistoval). || Chotěboř = Spartak Chotěboř (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Havlíčkův Brod). S-P = Semily-Pardubice. city Chotěboř.</t>
+          <t>B-tým Spartak Chotěboř (CLUB_S1953_54_0316). Přejmenováno II → B (D21). prev na 52/53 0263 (A-tým, B 52/53 neexistoval). || Chotěboř = Spartak Chotěboř (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Havlíčkův Brod). S-P = Semily-Pardubice. city Chotěboř. || TBD: auto-prev_club_id (D42/city) → CLUB_S2005_06_0166 'HC Chotěboř (STČ)'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -27908,12 +28098,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -28370,12 +28560,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -28925,7 +29115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28979,12 +29169,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0003</t>
+          <t>CLUB_S2006_07_0010</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28999,12 +29189,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0010</t>
+          <t>CLUB_S2006_07_0018</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29019,12 +29209,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0015</t>
+          <t>CLUB_S2006_07_0027</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29039,12 +29229,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0017</t>
+          <t>CLUB_S2006_07_0043</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29059,12 +29249,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0018</t>
+          <t>CLUB_S2006_07_0044</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29079,12 +29269,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0027</t>
+          <t>CLUB_S2006_07_0059</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29099,12 +29289,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0032</t>
+          <t>CLUB_S2006_07_0066</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29119,12 +29309,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0043</t>
+          <t>CLUB_S2006_07_0103</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29139,12 +29329,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0044</t>
+          <t>CLUB_S2006_07_0120</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -29159,12 +29349,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0059</t>
+          <t>CLUB_S2006_07_0136</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29179,12 +29369,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0066</t>
+          <t>CLUB_S2006_07_0141</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2005_06_0148 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -29199,12 +29389,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0083</t>
+          <t>CLUB_S2006_07_0146</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -29219,12 +29409,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0090</t>
+          <t>CLUB_S2006_07_0152</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Felbabka' → 'Králův Dvůr' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29239,12 +29429,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0091</t>
+          <t>CLUB_S2006_07_0157</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29259,12 +29449,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0103</t>
+          <t>CLUB_S2006_07_0165</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S2005_06_0166 'HC Chotěboř (STČ)'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -29279,12 +29469,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0103</t>
+          <t>CLUB_S2006_07_0168</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -29299,12 +29489,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0106</t>
+          <t>CLUB_S2006_07_0171</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29319,12 +29509,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0120</t>
+          <t>CLUB_S2006_07_0183</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29339,12 +29529,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0136</t>
+          <t>CLUB_S2006_07_0184</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29359,12 +29549,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0141</t>
+          <t>CLUB_S2006_07_0188</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2005_06_0148 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29379,217 +29569,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2006_07_0146</t>
+          <t>CLUB_S2006_07_0200</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CLUB_S2006_07_0152</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CLUB_S2006_07_0157</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CLUB_S2006_07_0168</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CLUB_S2006_07_0171</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CLUB_S2006_07_0180</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CLUB_S2006_07_0183</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S2006_07_0184</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S2006_07_0188</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S2006_07_0191</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S2006_07_0200</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F32"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -12394,7 +12394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12458,6 +12458,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15894,8 +15904,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -16025,7 +16033,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>

--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -12646,6 +12646,16 @@
           <t>NODE_S2006_07_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12660,6 +12670,14 @@
         <is>
           <t>NODE_S2005_06_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -12834,6 +12852,16 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12848,6 +12876,14 @@
         <is>
           <t>NODE_S2005_06_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -12928,6 +12964,16 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12942,6 +12988,14 @@
         <is>
           <t>NODE_S2005_06_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -12975,6 +13029,16 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12989,6 +13053,14 @@
         <is>
           <t>NODE_S2005_06_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -13022,6 +13094,8 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13036,6 +13110,14 @@
         <is>
           <t>NODE_S2005_06_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -13069,6 +13151,8 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13083,6 +13167,14 @@
         <is>
           <t>NODE_S2005_06_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -13116,6 +13208,8 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13130,6 +13224,14 @@
         <is>
           <t>NODE_S2005_06_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -13163,6 +13265,8 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13177,6 +13281,14 @@
         <is>
           <t>NODE_S2005_06_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -13210,6 +13322,8 @@
           <t>NODE_S2006_07_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13224,6 +13338,14 @@
         <is>
           <t>NODE_S2005_06_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -13257,6 +13379,8 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13271,6 +13395,14 @@
         <is>
           <t>NODE_S2005_06_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -13304,6 +13436,8 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13318,6 +13452,14 @@
         <is>
           <t>NODE_S2005_06_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -13351,6 +13493,16 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13365,6 +13517,14 @@
         <is>
           <t>NODE_S2005_06_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -13492,6 +13652,16 @@
           <t>NODE_S2006_07_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13506,6 +13676,14 @@
         <is>
           <t>NODE_S2005_06_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -13539,6 +13717,16 @@
           <t>NODE_S2006_07_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13553,6 +13741,14 @@
         <is>
           <t>NODE_S2005_06_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -13586,6 +13782,12 @@
           <t>NODE_S2006_07_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13600,6 +13802,14 @@
         <is>
           <t>NODE_S2005_06_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -13633,6 +13843,12 @@
           <t>NODE_S2006_07_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13647,6 +13863,14 @@
         <is>
           <t>NODE_S2005_06_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -13680,6 +13904,8 @@
           <t>NODE_S2006_07_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13694,6 +13920,14 @@
         <is>
           <t>NODE_S2005_06_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -13727,6 +13961,8 @@
           <t>NODE_S2006_07_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13741,6 +13977,14 @@
         <is>
           <t>NODE_S2005_06_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -14140,6 +14384,12 @@
           <t>NODE_S2006_07_0033</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0037</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14154,6 +14404,14 @@
         <is>
           <t>NODE_S2005_06_0039</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -14187,6 +14445,12 @@
           <t>NODE_S2006_07_0033</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0038</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14201,6 +14465,14 @@
         <is>
           <t>NODE_S2005_06_0040</t>
         </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -14234,6 +14506,8 @@
           <t>NODE_S2006_07_0033</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14248,6 +14522,14 @@
         <is>
           <t>NODE_S2005_06_0041</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -14375,6 +14657,8 @@
           <t>NODE_S2006_07_0033</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14389,6 +14673,14 @@
         <is>
           <t>NODE_S2005_06_0044</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -14516,6 +14808,12 @@
           <t>NODE_S2006_07_0033</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0036</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14530,6 +14828,14 @@
         <is>
           <t>NODE_S2005_06_0047</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -14610,6 +14916,12 @@
           <t>NODE_S2006_07_0045</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0047</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14619,6 +14931,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -14652,6 +14972,8 @@
           <t>NODE_S2006_07_0045</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14661,6 +14983,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -14689,6 +15019,12 @@
           <t>REG_JHC</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0049</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14708,6 +15044,14 @@
         <is>
           <t>NODE_S2005_06_0049</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -14741,6 +15085,8 @@
           <t>NODE_S2006_07_0048</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14755,6 +15101,14 @@
         <is>
           <t>NODE_S2005_06_0051</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -15102,6 +15456,12 @@
           <t>NODE_S2006_07_0056</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0058</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15116,6 +15476,14 @@
         <is>
           <t>NODE_S2005_06_0064</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -15149,6 +15517,8 @@
           <t>NODE_S2006_07_0056</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15158,6 +15528,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -15317,6 +15695,8 @@
           <t>NODE_S2006_07_0056</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15326,6 +15706,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -15406,6 +15794,12 @@
           <t>NODE_S2006_07_0063</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0067</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15420,6 +15814,14 @@
         <is>
           <t>NODE_S2005_06_0067</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -15537,6 +15939,8 @@
           <t>NODE_S2006_07_0063</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15546,6 +15950,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -15626,6 +16038,12 @@
           <t>NODE_S2006_07_0068</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0070</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15640,6 +16058,14 @@
         <is>
           <t>NODE_S2005_06_0071</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>5 týmů</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -15673,6 +16099,8 @@
           <t>NODE_S2006_07_0068</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15687,6 +16115,14 @@
         <is>
           <t>NODE_S2005_06_0072</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -15762,6 +16198,12 @@
           <t>NODE_S2006_07_0071</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0073</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15771,6 +16213,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -15804,6 +16254,8 @@
           <t>NODE_S2006_07_0071</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15813,6 +16265,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -15846,6 +16306,8 @@
           <t>NODE_S2006_07_0071</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15855,6 +16317,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -15904,6 +16374,8 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -16033,6 +16505,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>

--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -985,6 +985,11 @@
           <t>HC Sparta Praha (C)</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F8" t="n">
         <v>52</v>
       </c>
@@ -13094,8 +13099,6 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13151,8 +13154,6 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13208,8 +13209,6 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13265,8 +13264,6 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13322,8 +13319,6 @@
           <t>NODE_S2006_07_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13379,8 +13374,6 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13436,8 +13429,6 @@
           <t>NODE_S2006_07_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13787,7 +13778,6 @@
           <t>NODE_S2006_07_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13848,7 +13838,6 @@
           <t>NODE_S2006_07_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13904,8 +13893,6 @@
           <t>NODE_S2006_07_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13961,8 +13948,6 @@
           <t>NODE_S2006_07_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14389,7 +14374,6 @@
           <t>NODE_S2006_07_0037</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14450,7 +14434,6 @@
           <t>NODE_S2006_07_0038</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14506,8 +14489,6 @@
           <t>NODE_S2006_07_0033</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14657,8 +14638,6 @@
           <t>NODE_S2006_07_0033</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14813,7 +14792,6 @@
           <t>NODE_S2006_07_0036</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14921,7 +14899,6 @@
           <t>NODE_S2006_07_0047</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14972,8 +14949,6 @@
           <t>NODE_S2006_07_0045</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15024,7 +14999,6 @@
           <t>NODE_S2006_07_0049</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15085,8 +15059,6 @@
           <t>NODE_S2006_07_0048</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15461,7 +15433,6 @@
           <t>NODE_S2006_07_0058</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15517,8 +15488,6 @@
           <t>NODE_S2006_07_0056</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15695,8 +15664,6 @@
           <t>NODE_S2006_07_0056</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15799,7 +15766,6 @@
           <t>NODE_S2006_07_0067</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15939,8 +15905,6 @@
           <t>NODE_S2006_07_0063</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16043,7 +16007,6 @@
           <t>NODE_S2006_07_0070</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16099,8 +16062,6 @@
           <t>NODE_S2006_07_0068</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16203,7 +16164,6 @@
           <t>NODE_S2006_07_0073</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16254,8 +16214,6 @@
           <t>NODE_S2006_07_0071</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16306,8 +16264,6 @@
           <t>NODE_S2006_07_0071</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16374,8 +16330,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -16505,7 +16459,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -29401,7 +29354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29581,6 +29534,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Sparta Praha</t>
         </is>
       </c>
     </row>

--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -16330,6 +16330,8 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -16459,6 +16461,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>

--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +86,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -95,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +115,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -19095,8 +19106,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -19226,7 +19235,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -34898,7 +34906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -34955,7 +34963,7 @@
           <t>CLUB_S2006_07_0010</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34975,7 +34983,7 @@
           <t>CLUB_S2006_07_0018</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34995,7 +35003,7 @@
           <t>CLUB_S2006_07_0027</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35015,7 +35023,7 @@
           <t>CLUB_S2006_07_0043</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -35035,7 +35043,7 @@
           <t>CLUB_S2006_07_0044</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35055,7 +35063,7 @@
           <t>CLUB_S2006_07_0059</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35075,7 +35083,7 @@
           <t>CLUB_S2006_07_0066</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35095,7 +35103,7 @@
           <t>CLUB_S2006_07_0103</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35115,7 +35123,7 @@
           <t>CLUB_S2006_07_0120</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -35135,7 +35143,7 @@
           <t>CLUB_S2006_07_0136</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35155,7 +35163,7 @@
           <t>CLUB_S2006_07_0141</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2005_06_0148 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -35175,7 +35183,7 @@
           <t>CLUB_S2006_07_0146</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -35195,7 +35203,7 @@
           <t>CLUB_S2006_07_0152</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35215,7 +35223,7 @@
           <t>CLUB_S2006_07_0157</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35235,7 +35243,7 @@
           <t>CLUB_S2006_07_0165</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id (D42/city) → CLUB_S2005_06_0166 'HC Chotěboř (STČ)'; ověřit [fix_broken_prev_d42]</t>
         </is>
@@ -35255,7 +35263,7 @@
           <t>CLUB_S2006_07_0168</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -35275,7 +35283,7 @@
           <t>CLUB_S2006_07_0171</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35295,7 +35303,7 @@
           <t>CLUB_S2006_07_0183</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -35315,7 +35323,7 @@
           <t>CLUB_S2006_07_0184</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -35335,7 +35343,7 @@
           <t>CLUB_S2006_07_0188</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35355,11 +35363,37 @@
           <t>CLUB_S2006_07_0200</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga · NODE_S2006_07_0078</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Chotěboř, SB Světlá nad Sázavou), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F22"/>

--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,6 +117,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14865,7 +14868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15159,6 +15162,23 @@
         </is>
       </c>
       <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0078</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Chotěboř, SB Světlá nad Sázavou), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -35383,7 +35403,7 @@
           <t>Pardubický – Krajská liga · NODE_S2006_07_0078</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Chotěboř, SB Světlá nad Sázavou), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -16870,7 +16870,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Finále</t>
+          <t>Středočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Finále</t>
+          <t>Jihočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -17971,7 +17971,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Ústecký L40 Základní část</t>
+          <t>Ústecký, 4. úroveň, Základní část</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -18013,7 +18013,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40 základní část</t>
+          <t>Karlovarský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -18154,7 +18154,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 základní část</t>
+          <t>Hradecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 Finále</t>
+          <t>Hradecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina B</t>
+          <t>Hradecký, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -18353,7 +18353,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina A</t>
+          <t>Hradecký, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -18395,7 +18395,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina B</t>
+          <t>Hradecký, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 Finále</t>
+          <t>Hradecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Základní část</t>
+          <t>Pardubický, 4. úroveň, Základní část</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina A</t>
+          <t>Pardubický, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina B</t>
+          <t>Pardubický, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -18775,7 +18775,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Vysočina L40 Základní část</t>
+          <t>Vysočina, 4. úroveň, Základní část</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Vysočina L40 Finále</t>
+          <t>Vysočina, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Základní část</t>
+          <t>Jihomoravský, 4. úroveň, Základní část</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -18987,7 +18987,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -19126,6 +19126,8 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -19158,7 +19160,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -19255,6 +19257,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>

--- a/data/S2006_07_FINAL.xlsx
+++ b/data/S2006_07_FINAL.xlsx
@@ -5099,7 +5099,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -19126,8 +19126,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -19257,7 +19255,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
